--- a/data/nfm_dallyeong.xlsx
+++ b/data/nfm_dallyeong.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>seq</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>image_urls</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,7 +506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>품 : 54 길이 : 126 화장 : 121</t>
+          <t>화장 : 121 길이 : 126 품 : 54</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -516,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8333540.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333540.do</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -527,6 +532,11 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>PS0100200100102806300000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333540.do</t>
         </is>
       </c>
     </row>
@@ -573,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8517967.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8517967.do</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -584,6 +594,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>PS0100200100102806400000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8517967.do</t>
         </is>
       </c>
     </row>
@@ -610,7 +625,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8395307.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,6 +656,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>PS0100200100104555500000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do; https://www.nfm.go.kr/common/apiimage/relic/8395307.do; https://www.nfm.go.kr/common/apiimage/relic/8395308.do; https://www.nfm.go.kr/common/apiimage/relic/8395309.do</t>
         </is>
       </c>
     </row>
@@ -672,7 +692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>품 : 50 화장 : 118 길이 : 136</t>
+          <t>화장 : 118 길이 : 136 품 : 50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -687,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8411003.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8411003.do</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -698,6 +718,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>PS0100200100107759300000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8411003.do</t>
         </is>
       </c>
     </row>
@@ -729,7 +754,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>품 : 52.5 길이 : 129 화장 : 125</t>
+          <t>길이 : 129 화장 : 125 품 : 52.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -744,7 +769,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8381309.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8381309.do</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -755,6 +780,11 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>PS0100200100104555300000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8381309.do; https://www.nfm.go.kr/common/apiimage/relic/8381312.do</t>
         </is>
       </c>
     </row>
@@ -781,7 +811,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +831,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8561503.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -812,6 +842,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>PS0100200100104555400000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do; https://www.nfm.go.kr/common/apiimage/relic/8561501.do; https://www.nfm.go.kr/common/apiimage/relic/8561502.do; https://www.nfm.go.kr/common/apiimage/relic/8561503.do</t>
         </is>
       </c>
     </row>
@@ -843,7 +878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>품 : 59 길이 : 132 화장 : 127</t>
+          <t>길이 : 132 화장 : 127 품 : 59</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -858,7 +893,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8333495.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333495.do</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -869,6 +904,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>PS0100200100102806500000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333495.do</t>
         </is>
       </c>
     </row>
@@ -900,7 +940,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>화장 : 114 길이 : 125 품 : 56</t>
+          <t>품 : 56 길이 : 125 화장 : 114</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -915,7 +955,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8271731.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271732.do</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -926,6 +966,11 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>PS0100200100100978200000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271732.do; https://www.nfm.go.kr/common/apiimage/relic/8271730.do; https://www.nfm.go.kr/common/apiimage/relic/8271731.do</t>
         </is>
       </c>
     </row>
@@ -957,7 +1002,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>길이 : 138.5 화장 : 127.5</t>
+          <t>화장 : 127.5 길이 : 138.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -972,7 +1017,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8403056.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8403056.do</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -983,6 +1028,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>PS0100200100900109500000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8403056.do</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8443996.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8443996.do</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1040,6 +1090,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>PS0100200100107511100000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8443996.do</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>품 : 57 화장 : 82 길이 : 125</t>
+          <t>화장 : 82 길이 : 125 품 : 57</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1086,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8507198.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8507198.do</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1097,6 +1152,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>PS0100200100109054800000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8507198.do; https://www.nfm.go.kr/common/apiimage/relic/8507199.do; https://www.nfm.go.kr/common/apiimage/relic/8507197.do</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1188,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>품 : 56 길이 : 123 화장 : 97</t>
+          <t>화장 : 97 품 : 56 길이 : 123</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1143,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8529543.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8529543.do</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1154,6 +1214,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>PS0100200100100032500000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8529543.do</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8494859.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8494859.do</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1211,6 +1276,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>PS0100200100100097400000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8494859.do</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1312,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>길이 : 116.5 화장 : 87.5 품 : 47.5</t>
+          <t>길이 : 116.5 품 : 47.5 화장 : 87.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1257,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8250621.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8250621.do</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1268,6 +1338,11 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>PS0100200100100192300000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8250621.do</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1374,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>화장 : 92 길이 : 121.5 품 : 52</t>
+          <t>품 : 52 화장 : 92 길이 : 121.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1314,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8530693.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8530693.do</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1325,6 +1400,11 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>PS0100200100100240900000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8530693.do</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>화장 : 87.5 품 : 45 길이 : 119.5</t>
+          <t>길이 : 119.5 화장 : 87.5 품 : 45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1371,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8243226.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8243226.do</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1382,6 +1462,11 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>PS0100200100100489600000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8243226.do</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1498,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>길이 : 116 품 : 46 화장 : 94</t>
+          <t>화장 : 94 길이 : 116 품 : 46</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1428,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8495893.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8495893.do</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1439,6 +1524,11 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>PS0100200100100499900000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8495893.do</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1560,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>화장 : 79 길이 : 120 품 : 49.5</t>
+          <t>화장 : 79 품 : 49.5 길이 : 120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8273339.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273339.do</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1496,6 +1586,11 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>PS0100200100100508200000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273339.do</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1622,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>길이 : 114 품 : 54 화장 : 70</t>
+          <t>길이 : 114 화장 : 70 품 : 54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1542,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8311414.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8311414.do</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1553,6 +1648,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>PS0100200100100588200000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8311414.do</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1684,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>화장 : 87.5 길이 : 123 품 : 51.5</t>
+          <t>화장 : 87.5 품 : 51.5 길이 : 123</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1599,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8248879.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8248879.do</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1610,6 +1710,11 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>PS0100200100100590700000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8248879.do</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8510276.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8510276.do</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1667,6 +1772,11 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>PS0100200100100635200000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8510276.do</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1808,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>화장 : 99 품 : 59 길이 : 114</t>
+          <t>품 : 59 길이 : 114 화장 : 99</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1713,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8249401.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8249401.do</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1724,6 +1834,11 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>PS0100200100100635300000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8249401.do</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8312161.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8312161.do</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1781,6 +1896,11 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>PS0100200100100726900000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8312161.do</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1932,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>품 : 55 화장 : 82 길이 : 120</t>
+          <t>길이 : 120 품 : 55 화장 : 82</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8535034.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8535034.do</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1838,6 +1958,11 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>PS0100200100100953200000</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8535034.do</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1994,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>화장 : 130 길이 : 117.5 품 : 66</t>
+          <t>길이 : 117.5 품 : 66 화장 : 130</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1884,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8297874.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1895,6 +2020,11 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>PS0100200100100964900000</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do; https://www.nfm.go.kr/common/apiimage/relic/8297874.do; https://www.nfm.go.kr/common/apiimage/relic/8297872.do</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8395624.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1952,6 +2082,11 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>PS0100200100102096000000</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do; https://www.nfm.go.kr/common/apiimage/relic/8395625.do</t>
         </is>
       </c>
     </row>
@@ -1998,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8283074.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2009,6 +2144,11 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>PS0100200100102096100000</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do; https://www.nfm.go.kr/common/apiimage/relic/8283075.do</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2180,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>품 : 60 화장 : 113 길이 : 128</t>
+          <t>품 : 60 길이 : 128 화장 : 113</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2055,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8312910.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8312910.do</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2066,6 +2206,11 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>PS0100200100102438100000</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8312910.do</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2242,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>길이 : 120 품 : 72 화장 : 102</t>
+          <t>화장 : 102 품 : 72 길이 : 120</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2112,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8333267.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333267.do</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2123,6 +2268,11 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>PS0100200100102801700000</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333267.do; https://www.nfm.go.kr/common/apiimage/relic/8333268.do</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8333365.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333365.do</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2180,6 +2330,11 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>PS0100200100102802300000</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8333365.do</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>화장 : 92 품 : 57 등길이 : 123.5</t>
+          <t>등길이 : 123.5 품 : 57 화장 : 92</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2226,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8347753.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347752.do</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2237,6 +2392,11 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>PS0100200100103186100000</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347752.do; https://www.nfm.go.kr/common/apiimage/relic/8347753.do</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8347561.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347561.do</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2294,6 +2454,11 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>PS0100200100103454300000</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347561.do</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2490,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>품 : 50 길이 : 124 화장 : 92</t>
+          <t>품 : 50 화장 : 92 길이 : 124</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2340,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8354978.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8354978.do</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2351,6 +2516,11 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>PS0100200100103455500000</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8354978.do</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2552,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>화장 : 69 품 : 48 길이 : 120</t>
+          <t>길이 : 120 품 : 48 화장 : 69</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2397,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8560146.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8560146.do</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2408,6 +2578,11 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>PS0100200100103455600000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8560146.do</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2614,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>화장 : 85 길이 : 126</t>
+          <t>길이 : 126 화장 : 85</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2454,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8347566.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347566.do</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2465,6 +2640,11 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>PS0100200100103455700000</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8347566.do</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2676,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>품 : 57 화장 : 77 등길이 : 121</t>
+          <t>품 : 57 등길이 : 121 화장 : 77</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2511,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8548072.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548072.do</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2522,6 +2702,11 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>PS0100200100104232100000</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8548072.do</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8427645.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2579,6 +2764,11 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>PS0100200100106602900000</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do; https://www.nfm.go.kr/common/apiimage/relic/8427647.do; https://www.nfm.go.kr/common/apiimage/relic/8427645.do</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2800,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>화장 : 72 등길이 : 115 품 : 61</t>
+          <t>화장 : 72 품 : 61 등길이 : 115</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2625,7 +2815,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8430574.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2636,6 +2826,11 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>PS0100200100106718600000</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do; https://www.nfm.go.kr/common/apiimage/relic/8430574.do; https://www.nfm.go.kr/common/apiimage/relic/8430572.do</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2877,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8430046.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430046.do</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2693,6 +2888,11 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>PS0100200100106746700000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430046.do</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2924,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>길이 : 130 품 : 49.5 화장 : 92.5</t>
+          <t>화장 : 92.5 길이 : 130 품 : 49.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2739,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8445951.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8445951.do</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2750,6 +2950,11 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>PS0100200100107080100000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8445951.do</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2986,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>화장 : 93.5 품 : 49 길이 : 122</t>
+          <t>품 : 49 화장 : 93.5 길이 : 122</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2796,7 +3001,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8446720.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8446720.do</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2807,6 +3012,11 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>PS0100200100107081700000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8446720.do</t>
         </is>
       </c>
     </row>
@@ -2838,7 +3048,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>품 : 50 화장 : 102.5 등길이 : 126</t>
+          <t>등길이 : 126 품 : 50 화장 : 102.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2853,7 +3063,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8440142.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8440142.do</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2864,6 +3074,11 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>PS0100200100107226000000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8440142.do</t>
         </is>
       </c>
     </row>
@@ -2895,7 +3110,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>화장 : 90 길이 : 133.5 품 : 68</t>
+          <t>품 : 68 화장 : 90 길이 : 133.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2910,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8385172.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8385172.do</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2921,6 +3136,11 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>PS0100200100107745700000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8385172.do</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3172,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>길이 : 124 품 : 71 화장 : 115</t>
+          <t>화장 : 115 길이 : 124 품 : 71</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2967,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8572397.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8572397.do</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2978,6 +3198,11 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>PS0100200100107753400000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8572397.do</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3234,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>화장 : 75 품 : 58 길이 : 127.5</t>
+          <t>화장 : 75 길이 : 127.5 품 : 58</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3024,7 +3249,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8484672.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3035,6 +3260,11 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>PS0100200100109486500000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do; https://www.nfm.go.kr/common/apiimage/relic/8484673.do; https://www.nfm.go.kr/common/apiimage/relic/8484671.do</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3296,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>진동 : 32 화장 : 89 길이 : 130</t>
+          <t>길이 : 130 화장 : 89 진동 : 32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3081,7 +3311,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8293640.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8293640.do</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3092,6 +3322,11 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>PS0100200100700051400000</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8293640.do</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8301643.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8301643.do</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3149,6 +3384,11 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>PS0100200100900077200000</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8301643.do</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8309922.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8309922.do</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3206,6 +3446,11 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>PS0100200100900118300000</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8309922.do</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3482,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>품 : 61 길이 : 138.2 화장 : 92.5</t>
+          <t>길이 : 138.2 화장 : 92.5 품 : 61</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3252,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8309243.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8309243.do</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3263,6 +3508,11 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>PS0100200100900118600000</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8309243.do</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3544,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>품 : 54 화장 : 88.5 길이 : 100.5</t>
+          <t>화장 : 88.5 길이 : 100.5 품 : 54</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3309,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8525811.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8525811.do</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3320,6 +3570,11 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>PS0100200100102387900000</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8525811.do</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3606,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>화장 : 94.5 품 : 57.5 길이 : 98</t>
+          <t>품 : 57.5 화장 : 94.5 길이 : 98</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3366,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8314559.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8314559.do</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3377,6 +3632,11 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>PS0100200100102388000000</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8314559.do; https://www.nfm.go.kr/common/apiimage/relic/8314560.do</t>
         </is>
       </c>
     </row>

--- a/data/nfm_dallyeong.xlsx
+++ b/data/nfm_dallyeong.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>화장 : 121 길이 : 126 품 : 54</t>
+          <t>품 : 54 화장 : 121 길이 : 126</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>화장 : 120.5 길이 : 125 품 : 57</t>
+          <t>화장 : 120.5 품 : 57 길이 : 125</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
+          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>길이 : 131.5 품 : 55 화장 : 125.5</t>
+          <t>품 : 55 길이 : 131.5 화장 : 125.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395308.do</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395306.do; https://www.nfm.go.kr/common/apiimage/relic/8395307.do; https://www.nfm.go.kr/common/apiimage/relic/8395308.do; https://www.nfm.go.kr/common/apiimage/relic/8395309.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395308.do; https://www.nfm.go.kr/common/apiimage/relic/8395306.do; https://www.nfm.go.kr/common/apiimage/relic/8395309.do; https://www.nfm.go.kr/common/apiimage/relic/8395307.do</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>화장 : 118 길이 : 136 품 : 50</t>
+          <t>길이 : 136 화장 : 118 품 : 50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>사회생활-의례생활-상장 / 의-의류-평상복-남자포류</t>
+          <t>의-의류-평상복-남자포류 / 사회생활-의례생활-상장</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>길이 : 129.5 품 : 57 화장 : 127.5</t>
+          <t>품 : 57 길이 : 129.5 화장 : 127.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561501.do</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8561504.do; https://www.nfm.go.kr/common/apiimage/relic/8561501.do; https://www.nfm.go.kr/common/apiimage/relic/8561502.do; https://www.nfm.go.kr/common/apiimage/relic/8561503.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8561501.do; https://www.nfm.go.kr/common/apiimage/relic/8561504.do; https://www.nfm.go.kr/common/apiimage/relic/8561502.do; https://www.nfm.go.kr/common/apiimage/relic/8561503.do</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>길이 : 132 화장 : 127 품 : 59</t>
+          <t>품 : 59 화장 : 127 길이 : 132</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>품 : 56 길이 : 125 화장 : 114</t>
+          <t>화장 : 114 길이 : 125 품 : 56</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>화장 : 127.5 길이 : 138.5</t>
+          <t>길이 : 138.5 화장 : 127.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>등길이 : 124 품 : 50.5 화장 : 97.5</t>
+          <t>품 : 50.5 화장 : 97.5 등길이 : 124</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>화장 : 82 길이 : 125 품 : 57</t>
+          <t>길이 : 125 품 : 57 화장 : 82</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>화장 : 97 품 : 56 길이 : 123</t>
+          <t>품 : 56 길이 : 123 화장 : 97</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>길이 : 126.5 품 : 50 화장 : 89</t>
+          <t>품 : 50 화장 : 89 길이 : 126.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>품 : 52 화장 : 92 길이 : 121.5</t>
+          <t>길이 : 121.5 화장 : 92 품 : 52</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>길이 : 119.5 화장 : 87.5 품 : 45</t>
+          <t>길이 : 119.5 품 : 45 화장 : 87.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>화장 : 94 길이 : 116 품 : 46</t>
+          <t>길이 : 116 품 : 46 화장 : 94</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>화장 : 79 품 : 49.5 길이 : 120</t>
+          <t>품 : 49.5 길이 : 120 화장 : 79</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>품 : 47.5 화장 : 86 길이 : 121</t>
+          <t>길이 : 121 화장 : 86 품 : 47.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>품 : 59 길이 : 114 화장 : 99</t>
+          <t>화장 : 99 품 : 59 길이 : 114</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>길이 : 120 품 : 55 화장 : 82</t>
+          <t>길이 : 120 화장 : 82 품 : 55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>길이 : 117.5 품 : 66 화장 : 130</t>
+          <t>길이 : 117.5 화장 : 130 품 : 66</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8297872.do</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8297873.do; https://www.nfm.go.kr/common/apiimage/relic/8297874.do; https://www.nfm.go.kr/common/apiimage/relic/8297872.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8297872.do; https://www.nfm.go.kr/common/apiimage/relic/8297873.do; https://www.nfm.go.kr/common/apiimage/relic/8297874.do</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395625.do</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8395624.do; https://www.nfm.go.kr/common/apiimage/relic/8395625.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8395625.do; https://www.nfm.go.kr/common/apiimage/relic/8395624.do</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>길이 : 140.5 품 : 68 화장 : 122.5</t>
+          <t>품 : 68 화장 : 122.5 길이 : 140.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8283075.do</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8283074.do; https://www.nfm.go.kr/common/apiimage/relic/8283075.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8283075.do; https://www.nfm.go.kr/common/apiimage/relic/8283074.do</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>화장 : 128.5 길이 : 124 품 : 74</t>
+          <t>품 : 74 화장 : 128.5 길이 : 124</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>등길이 : 123.5 품 : 57 화장 : 92</t>
+          <t>등길이 : 123.5 화장 : 92 품 : 57</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>화장 : 77.5 길이 : 126</t>
+          <t>길이 : 126 화장 : 77.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>품 : 50 화장 : 92 길이 : 124</t>
+          <t>품 : 50 길이 : 124 화장 : 92</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>길이 : 120 품 : 48 화장 : 69</t>
+          <t>품 : 48 화장 : 69 길이 : 120</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>길이 : 126 화장 : 85</t>
+          <t>화장 : 85 길이 : 126</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>품 : 57 등길이 : 123 화장 : 81</t>
+          <t>화장 : 81 등길이 : 123 품 : 57</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8427645.do</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8427646.do; https://www.nfm.go.kr/common/apiimage/relic/8427647.do; https://www.nfm.go.kr/common/apiimage/relic/8427645.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8427645.do; https://www.nfm.go.kr/common/apiimage/relic/8427646.do; https://www.nfm.go.kr/common/apiimage/relic/8427647.do</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>화장 : 72 품 : 61 등길이 : 115</t>
+          <t>품 : 61 화장 : 72 등길이 : 115</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430572.do</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8430573.do; https://www.nfm.go.kr/common/apiimage/relic/8430574.do; https://www.nfm.go.kr/common/apiimage/relic/8430572.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8430572.do; https://www.nfm.go.kr/common/apiimage/relic/8430573.do; https://www.nfm.go.kr/common/apiimage/relic/8430574.do</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>화장 : 82 등길이 : 125 품 : 64</t>
+          <t>품 : 64 등길이 : 125 화장 : 82</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>화장 : 92.5 길이 : 130 품 : 49.5</t>
+          <t>화장 : 92.5 품 : 49.5 길이 : 130</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>등길이 : 126 품 : 50 화장 : 102.5</t>
+          <t>화장 : 102.5 품 : 50 등길이 : 126</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>품 : 68 화장 : 90 길이 : 133.5</t>
+          <t>길이 : 133.5 품 : 68 화장 : 90</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>화장 : 115 길이 : 124 품 : 71</t>
+          <t>길이 : 124 화장 : 115 품 : 71</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>화장 : 75 길이 : 127.5 품 : 58</t>
+          <t>화장 : 75 품 : 58 길이 : 127.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8484673.do</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8484672.do; https://www.nfm.go.kr/common/apiimage/relic/8484673.do; https://www.nfm.go.kr/common/apiimage/relic/8484671.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8484673.do; https://www.nfm.go.kr/common/apiimage/relic/8484672.do; https://www.nfm.go.kr/common/apiimage/relic/8484671.do</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>길이 : 130 화장 : 89 진동 : 32</t>
+          <t>길이 : 130 진동 : 32 화장 : 89</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>길이 : 128 화장 : 87.5 품 : 62</t>
+          <t>화장 : 87.5 길이 : 128 품 : 62</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>품 : 56 화장 : 89.5 길이 : 124.2</t>
+          <t>화장 : 89.5 품 : 56 길이 : 124.2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>길이 : 138.2 화장 : 92.5 품 : 61</t>
+          <t>화장 : 92.5 품 : 61 길이 : 138.2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>품 : 57.5 화장 : 94.5 길이 : 98</t>
+          <t>화장 : 94.5 품 : 57.5 길이 : 98</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
